--- a/risks.xlsx
+++ b/risks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\moodle\local\activities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2808BB75-A8DD-4CE2-AC82-588A54DE4F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8007515-0B90-4E36-A0DB-08E058EB1BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" firstSheet="1" activeTab="1" xr2:uid="{AD7C0EC4-A2F3-47F0-BC05-D404D6BD509F}"/>
   </bookViews>
@@ -2574,9 +2574,6 @@
     <t>Staff in Charge or delegated staff member to do a grounds safety check before the activity</t>
   </si>
   <si>
-    <t>Events || AV equipment</t>
-  </si>
-  <si>
     <t>Events || Event at External venue</t>
   </si>
   <si>
@@ -3123,6 +3120,9 @@
   </si>
   <si>
     <t>General Information that must be included on the activity form/risk assessment for K - 6</t>
+  </si>
+  <si>
+    <t>Events || AV Equipment</t>
   </si>
 </sst>
 </file>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="288" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="73" t="s">
-        <v>630</v>
+        <v>781</v>
       </c>
       <c r="B288" s="83" t="s">
         <v>459</v>
@@ -11626,7 +11626,7 @@
     </row>
     <row r="289" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="73" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B289" s="62" t="s">
         <v>88</v>
@@ -11650,7 +11650,7 @@
     </row>
     <row r="290" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="73" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B290" s="68" t="s">
         <v>272</v>
@@ -11674,22 +11674,22 @@
     </row>
     <row r="291" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="73" t="s">
+        <v>631</v>
+      </c>
+      <c r="B291" s="116" t="s">
         <v>632</v>
-      </c>
-      <c r="B291" s="116" t="s">
-        <v>633</v>
       </c>
       <c r="C291" s="147">
         <v>3</v>
       </c>
       <c r="D291" s="113" t="s">
+        <v>633</v>
+      </c>
+      <c r="E291" s="147">
+        <v>5</v>
+      </c>
+      <c r="F291" s="113" t="s">
         <v>634</v>
-      </c>
-      <c r="E291" s="147">
-        <v>5</v>
-      </c>
-      <c r="F291" s="113" t="s">
-        <v>635</v>
       </c>
       <c r="G291" s="62" t="s">
         <v>616</v>
@@ -11698,7 +11698,7 @@
     </row>
     <row r="292" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="73" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B292" s="117" t="s">
         <v>507</v>
@@ -11707,13 +11707,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="113" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E292" s="147">
         <v>5</v>
       </c>
       <c r="F292" s="113" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G292" s="62" t="s">
         <v>616</v>
@@ -11722,7 +11722,7 @@
     </row>
     <row r="293" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B293" s="83" t="s">
         <v>462</v>
@@ -11746,7 +11746,7 @@
     </row>
     <row r="294" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B294" s="83" t="s">
         <v>464</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="295" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B295" s="82" t="s">
         <v>467</v>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="296" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B296" s="82" t="s">
         <v>469</v>
@@ -11818,7 +11818,7 @@
     </row>
     <row r="297" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B297" s="82" t="s">
         <v>471</v>
@@ -11842,22 +11842,22 @@
     </row>
     <row r="298" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="73" t="s">
+        <v>637</v>
+      </c>
+      <c r="B298" s="82" t="s">
         <v>638</v>
-      </c>
-      <c r="B298" s="82" t="s">
-        <v>639</v>
       </c>
       <c r="C298" s="135">
         <v>2</v>
       </c>
       <c r="D298" s="83" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E298" s="135">
         <v>4</v>
       </c>
       <c r="F298" s="113" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G298" s="62" t="s">
         <v>616</v>
@@ -11866,40 +11866,40 @@
     </row>
     <row r="299" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="73" t="s">
+        <v>640</v>
+      </c>
+      <c r="B299" s="83" t="s">
         <v>641</v>
-      </c>
-      <c r="B299" s="83" t="s">
-        <v>642</v>
       </c>
       <c r="C299" s="135">
         <v>2</v>
       </c>
       <c r="D299" s="82" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E299" s="135">
         <v>4</v>
       </c>
       <c r="F299" s="82" t="s">
+        <v>643</v>
+      </c>
+      <c r="G299" s="82" t="s">
         <v>644</v>
-      </c>
-      <c r="G299" s="82" t="s">
-        <v>645</v>
       </c>
       <c r="H299" s="82"/>
     </row>
     <row r="300" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="119" t="s">
+        <v>645</v>
+      </c>
+      <c r="B300" s="82" t="s">
         <v>646</v>
-      </c>
-      <c r="B300" s="82" t="s">
-        <v>647</v>
       </c>
       <c r="C300" s="135">
         <v>2</v>
       </c>
       <c r="D300" s="113" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E300" s="135">
         <v>5</v>
@@ -11914,16 +11914,16 @@
     </row>
     <row r="301" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="119" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B301" s="82" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C301" s="135">
         <v>2</v>
       </c>
       <c r="D301" s="82" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E301" s="135">
         <v>5</v>
@@ -11938,16 +11938,16 @@
     </row>
     <row r="302" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="119" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B302" s="82" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C302" s="135">
         <v>2</v>
       </c>
       <c r="D302" s="82" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E302" s="135">
         <v>5</v>
@@ -11956,22 +11956,22 @@
         <v>233</v>
       </c>
       <c r="G302" s="82" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H302" s="82"/>
     </row>
     <row r="303" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="119" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B303" s="82" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C303" s="135">
         <v>2</v>
       </c>
       <c r="D303" s="82" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E303" s="135">
         <v>5</v>
@@ -11980,22 +11980,22 @@
         <v>233</v>
       </c>
       <c r="G303" s="82" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H303" s="82"/>
     </row>
     <row r="304" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="119" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B304" s="82" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C304" s="135">
         <v>2</v>
       </c>
       <c r="D304" s="82" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E304" s="135">
         <v>5</v>
@@ -12004,22 +12004,22 @@
         <v>233</v>
       </c>
       <c r="G304" s="82" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H304" s="82"/>
     </row>
     <row r="305" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="73" t="s">
+        <v>657</v>
+      </c>
+      <c r="B305" s="82" t="s">
         <v>658</v>
-      </c>
-      <c r="B305" s="82" t="s">
-        <v>659</v>
       </c>
       <c r="C305" s="135">
         <v>2</v>
       </c>
       <c r="D305" s="82" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E305" s="135">
         <v>4</v>
@@ -12028,16 +12028,16 @@
         <v>612</v>
       </c>
       <c r="G305" s="82" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H305" s="82"/>
     </row>
     <row r="306" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="73" t="s">
+        <v>660</v>
+      </c>
+      <c r="B306" s="82" t="s">
         <v>661</v>
-      </c>
-      <c r="B306" s="82" t="s">
-        <v>662</v>
       </c>
       <c r="C306" s="135">
         <v>4</v>
@@ -12052,16 +12052,16 @@
         <v>567</v>
       </c>
       <c r="G306" s="82" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H306" s="82"/>
     </row>
     <row r="307" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="73" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B307" s="82" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C307" s="135">
         <v>3</v>
@@ -12076,22 +12076,22 @@
         <v>567</v>
       </c>
       <c r="G307" s="82" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H307" s="82"/>
     </row>
     <row r="308" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="73" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B308" s="82" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C308" s="135">
         <v>3</v>
       </c>
       <c r="D308" s="113" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E308" s="135">
         <v>5</v>
@@ -12100,16 +12100,16 @@
         <v>567</v>
       </c>
       <c r="G308" s="82" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H308" s="82"/>
     </row>
     <row r="309" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="73" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B309" s="82" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C309" s="135">
         <v>4</v>
@@ -12124,16 +12124,16 @@
         <v>567</v>
       </c>
       <c r="G309" s="82" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H309" s="82"/>
     </row>
     <row r="310" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="73" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B310" s="82" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C310" s="135">
         <v>4</v>
@@ -12154,10 +12154,10 @@
     </row>
     <row r="311" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="73" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B311" s="82" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C311" s="135">
         <v>2</v>
@@ -12178,16 +12178,16 @@
     </row>
     <row r="312" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="73" t="s">
+        <v>668</v>
+      </c>
+      <c r="B312" s="82" t="s">
         <v>669</v>
-      </c>
-      <c r="B312" s="82" t="s">
-        <v>670</v>
       </c>
       <c r="C312" s="135">
         <v>3</v>
       </c>
       <c r="D312" s="82" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E312" s="135">
         <v>4</v>
@@ -12196,22 +12196,22 @@
         <v>124</v>
       </c>
       <c r="G312" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H312" s="82"/>
     </row>
     <row r="313" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B313" s="82" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C313" s="135">
         <v>2</v>
       </c>
       <c r="D313" s="82" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E313" s="135">
         <v>4</v>
@@ -12220,22 +12220,22 @@
         <v>124</v>
       </c>
       <c r="G313" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H313" s="82"/>
     </row>
     <row r="314" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B314" s="82" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C314" s="135">
         <v>3</v>
       </c>
       <c r="D314" s="82" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E314" s="135">
         <v>5</v>
@@ -12244,22 +12244,22 @@
         <v>124</v>
       </c>
       <c r="G314" s="82" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H314" s="82"/>
     </row>
     <row r="315" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B315" s="82" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C315" s="135">
         <v>3</v>
       </c>
       <c r="D315" s="82" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E315" s="135">
         <v>5</v>
@@ -12268,22 +12268,22 @@
         <v>124</v>
       </c>
       <c r="G315" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H315" s="82"/>
     </row>
     <row r="316" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B316" s="82" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C316" s="135">
         <v>2</v>
       </c>
       <c r="D316" s="82" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E316" s="135">
         <v>4</v>
@@ -12292,22 +12292,22 @@
         <v>124</v>
       </c>
       <c r="G316" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H316" s="82"/>
     </row>
     <row r="317" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B317" s="82" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C317" s="135">
         <v>3</v>
       </c>
       <c r="D317" s="82" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E317" s="135">
         <v>5</v>
@@ -12316,22 +12316,22 @@
         <v>124</v>
       </c>
       <c r="G317" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H317" s="82"/>
     </row>
     <row r="318" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B318" s="82" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C318" s="135">
         <v>3</v>
       </c>
       <c r="D318" s="82" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E318" s="135">
         <v>5</v>
@@ -12340,22 +12340,22 @@
         <v>124</v>
       </c>
       <c r="G318" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H318" s="82"/>
     </row>
     <row r="319" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B319" s="82" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C319" s="135">
         <v>2</v>
       </c>
       <c r="D319" s="82" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E319" s="135">
         <v>4</v>
@@ -12364,22 +12364,22 @@
         <v>124</v>
       </c>
       <c r="G319" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H319" s="82"/>
     </row>
     <row r="320" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B320" s="82" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C320" s="135">
         <v>3</v>
       </c>
       <c r="D320" s="82" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E320" s="135">
         <v>5</v>
@@ -12388,22 +12388,22 @@
         <v>124</v>
       </c>
       <c r="G320" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H320" s="82"/>
     </row>
     <row r="321" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B321" s="82" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C321" s="135">
         <v>2</v>
       </c>
       <c r="D321" s="82" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E321" s="135">
         <v>5</v>
@@ -12412,22 +12412,22 @@
         <v>124</v>
       </c>
       <c r="G321" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H321" s="82"/>
     </row>
     <row r="322" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B322" s="82" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C322" s="135">
         <v>3</v>
       </c>
       <c r="D322" s="82" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E322" s="135">
         <v>6</v>
@@ -12436,46 +12436,46 @@
         <v>124</v>
       </c>
       <c r="G322" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H322" s="82"/>
     </row>
     <row r="323" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B323" s="82" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C323" s="135">
         <v>2</v>
       </c>
       <c r="D323" s="82" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E323" s="135">
         <v>6</v>
       </c>
       <c r="F323" s="113" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G323" s="82" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H323" s="82"/>
     </row>
     <row r="324" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="73" t="s">
+        <v>696</v>
+      </c>
+      <c r="B324" s="82" t="s">
         <v>697</v>
-      </c>
-      <c r="B324" s="82" t="s">
-        <v>698</v>
       </c>
       <c r="C324" s="135">
         <v>2</v>
       </c>
       <c r="D324" s="82" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E324" s="135">
         <v>5</v>
@@ -12484,22 +12484,22 @@
         <v>233</v>
       </c>
       <c r="G324" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H324" s="82"/>
     </row>
     <row r="325" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B325" s="82" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C325" s="135">
         <v>2</v>
       </c>
       <c r="D325" s="82" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E325" s="135">
         <v>5</v>
@@ -12508,22 +12508,22 @@
         <v>124</v>
       </c>
       <c r="G325" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H325" s="82"/>
     </row>
     <row r="326" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B326" s="82" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C326" s="135">
         <v>3</v>
       </c>
       <c r="D326" s="82" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E326" s="135">
         <v>6</v>
@@ -12532,22 +12532,22 @@
         <v>233</v>
       </c>
       <c r="G326" s="82" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H326" s="82"/>
     </row>
     <row r="327" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B327" s="82" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C327" s="135">
         <v>4</v>
       </c>
       <c r="D327" s="82" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E327" s="135">
         <v>6</v>
@@ -12556,22 +12556,22 @@
         <v>233</v>
       </c>
       <c r="G327" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H327" s="82"/>
     </row>
     <row r="328" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B328" s="82" t="s">
+        <v>707</v>
+      </c>
+      <c r="C328" s="135">
+        <v>5</v>
+      </c>
+      <c r="D328" s="82" t="s">
         <v>708</v>
-      </c>
-      <c r="C328" s="135">
-        <v>5</v>
-      </c>
-      <c r="D328" s="82" t="s">
-        <v>709</v>
       </c>
       <c r="E328" s="135">
         <v>6</v>
@@ -12580,286 +12580,286 @@
         <v>536</v>
       </c>
       <c r="G328" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H328" s="82"/>
     </row>
     <row r="329" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B329" s="82" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C329" s="135">
         <v>3</v>
       </c>
       <c r="D329" s="82" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E329" s="135">
         <v>4</v>
       </c>
       <c r="F329" s="113" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G329" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H329" s="82"/>
     </row>
     <row r="330" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B330" s="82" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C330" s="135">
         <v>3</v>
       </c>
       <c r="D330" s="82" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E330" s="135">
         <v>4</v>
       </c>
       <c r="F330" s="113" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G330" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H330" s="82"/>
     </row>
     <row r="331" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B331" s="82" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C331" s="135">
         <v>3</v>
       </c>
       <c r="D331" s="82" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E331" s="135">
         <v>4</v>
       </c>
       <c r="F331" s="113" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G331" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H331" s="82"/>
     </row>
     <row r="332" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B332" s="82" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C332" s="135">
         <v>4</v>
       </c>
       <c r="D332" s="82" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E332" s="135">
         <v>4</v>
       </c>
       <c r="F332" s="113" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G332" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H332" s="82"/>
     </row>
     <row r="333" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B333" s="82" t="s">
+        <v>719</v>
+      </c>
+      <c r="C333" s="135">
+        <v>5</v>
+      </c>
+      <c r="D333" s="82" t="s">
         <v>720</v>
-      </c>
-      <c r="C333" s="135">
-        <v>5</v>
-      </c>
-      <c r="D333" s="82" t="s">
-        <v>721</v>
       </c>
       <c r="E333" s="135">
         <v>6</v>
       </c>
       <c r="F333" s="113" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G333" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H333" s="82"/>
     </row>
     <row r="334" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B334" s="82" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C334" s="135">
         <v>4</v>
       </c>
       <c r="D334" s="82" t="s">
+        <v>723</v>
+      </c>
+      <c r="E334" s="135">
+        <v>5</v>
+      </c>
+      <c r="F334" s="113" t="s">
         <v>724</v>
       </c>
-      <c r="E334" s="135">
-        <v>5</v>
-      </c>
-      <c r="F334" s="113" t="s">
-        <v>725</v>
-      </c>
       <c r="G334" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H334" s="82"/>
     </row>
     <row r="335" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B335" s="120" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C335" s="135">
         <v>3</v>
       </c>
       <c r="D335" s="82" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E335" s="135">
         <v>5</v>
       </c>
       <c r="F335" s="113" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G335" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H335" s="82"/>
     </row>
     <row r="336" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B336" s="82" t="s">
+        <v>727</v>
+      </c>
+      <c r="C336" s="135">
+        <v>5</v>
+      </c>
+      <c r="D336" s="82" t="s">
         <v>728</v>
-      </c>
-      <c r="C336" s="135">
-        <v>5</v>
-      </c>
-      <c r="D336" s="82" t="s">
-        <v>729</v>
       </c>
       <c r="E336" s="135">
         <v>6</v>
       </c>
       <c r="F336" s="113" t="s">
+        <v>729</v>
+      </c>
+      <c r="G336" s="82" t="s">
         <v>730</v>
-      </c>
-      <c r="G336" s="82" t="s">
-        <v>731</v>
       </c>
       <c r="H336" s="82"/>
     </row>
     <row r="337" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B337" s="82" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C337" s="135">
         <v>3</v>
       </c>
       <c r="D337" s="82" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E337" s="135">
         <v>6</v>
       </c>
       <c r="F337" s="113" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G337" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H337" s="82"/>
     </row>
     <row r="338" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B338" s="121" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C338" s="135">
         <v>2</v>
       </c>
       <c r="D338" s="82" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E338" s="135">
         <v>6</v>
       </c>
       <c r="F338" s="113" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G338" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H338" s="82"/>
     </row>
     <row r="339" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B339" s="82" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C339" s="135">
         <v>2</v>
       </c>
       <c r="D339" s="82" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E339" s="135">
         <v>6</v>
       </c>
       <c r="F339" s="113" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G339" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H339" s="82"/>
     </row>
     <row r="340" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B340" s="82" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C340" s="135">
         <v>3</v>
       </c>
       <c r="D340" s="82" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E340" s="135">
         <v>5</v>
@@ -12868,22 +12868,22 @@
         <v>233</v>
       </c>
       <c r="G340" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H340" s="82"/>
     </row>
     <row r="341" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B341" s="82" t="s">
+        <v>740</v>
+      </c>
+      <c r="C341" s="135">
+        <v>5</v>
+      </c>
+      <c r="D341" s="82" t="s">
         <v>741</v>
-      </c>
-      <c r="C341" s="135">
-        <v>5</v>
-      </c>
-      <c r="D341" s="82" t="s">
-        <v>742</v>
       </c>
       <c r="E341" s="135">
         <v>6</v>
@@ -12892,46 +12892,46 @@
         <v>233</v>
       </c>
       <c r="G341" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H341" s="82"/>
     </row>
     <row r="342" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B342" s="82" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C342" s="135">
         <v>2</v>
       </c>
       <c r="D342" s="82" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E342" s="135">
         <v>3</v>
       </c>
       <c r="F342" s="113" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G342" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H342" s="82"/>
     </row>
     <row r="343" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B343" s="82" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C343" s="135">
         <v>4</v>
       </c>
       <c r="D343" s="82" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E343" s="135">
         <v>5</v>
@@ -12940,22 +12940,22 @@
         <v>536</v>
       </c>
       <c r="G343" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H343" s="82"/>
     </row>
     <row r="344" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B344" s="82" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C344" s="135">
         <v>3</v>
       </c>
       <c r="D344" s="82" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E344" s="135">
         <v>4</v>
@@ -12964,22 +12964,22 @@
         <v>536</v>
       </c>
       <c r="G344" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H344" s="82"/>
     </row>
     <row r="345" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B345" s="114" t="s">
+        <v>749</v>
+      </c>
+      <c r="C345" s="148">
+        <v>5</v>
+      </c>
+      <c r="D345" s="114" t="s">
         <v>750</v>
-      </c>
-      <c r="C345" s="148">
-        <v>5</v>
-      </c>
-      <c r="D345" s="114" t="s">
-        <v>751</v>
       </c>
       <c r="E345" s="148">
         <v>6</v>
@@ -12988,22 +12988,22 @@
         <v>536</v>
       </c>
       <c r="G345" s="114" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H345" s="114"/>
     </row>
     <row r="346" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B346" s="82" t="s">
+        <v>751</v>
+      </c>
+      <c r="C346" s="135">
+        <v>5</v>
+      </c>
+      <c r="D346" s="82" t="s">
         <v>752</v>
-      </c>
-      <c r="C346" s="135">
-        <v>5</v>
-      </c>
-      <c r="D346" s="82" t="s">
-        <v>753</v>
       </c>
       <c r="E346" s="135">
         <v>6</v>
@@ -13012,22 +13012,22 @@
         <v>536</v>
       </c>
       <c r="G346" s="82" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H346" s="82"/>
     </row>
     <row r="347" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B347" s="82" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C347" s="135">
         <v>2</v>
       </c>
       <c r="D347" s="82" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E347" s="135">
         <v>5</v>
@@ -13036,22 +13036,22 @@
         <v>536</v>
       </c>
       <c r="G347" s="82" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H347" s="82"/>
     </row>
     <row r="348" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="73" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B348" s="82" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C348" s="135">
         <v>2</v>
       </c>
       <c r="D348" s="113" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E348" s="135">
         <v>5</v>
@@ -13060,22 +13060,22 @@
         <v>536</v>
       </c>
       <c r="G348" s="82" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H348" s="82"/>
     </row>
     <row r="349" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="92" t="s">
+        <v>758</v>
+      </c>
+      <c r="B349" s="82" t="s">
         <v>759</v>
-      </c>
-      <c r="B349" s="82" t="s">
-        <v>760</v>
       </c>
       <c r="C349" s="135">
         <v>2</v>
       </c>
       <c r="D349" s="82" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E349" s="135">
         <v>4</v>
@@ -13090,16 +13090,16 @@
     </row>
     <row r="350" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B350" s="82" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C350" s="135">
         <v>2</v>
       </c>
       <c r="D350" s="82" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E350" s="135">
         <v>5</v>
@@ -13114,16 +13114,16 @@
     </row>
     <row r="351" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B351" s="82" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C351" s="135">
         <v>2</v>
       </c>
       <c r="D351" s="82" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E351" s="135">
         <v>5</v>
@@ -13132,22 +13132,22 @@
         <v>597</v>
       </c>
       <c r="G351" s="82" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H351" s="82"/>
     </row>
     <row r="352" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B352" s="82" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C352" s="135">
         <v>2</v>
       </c>
       <c r="D352" s="82" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E352" s="135">
         <v>5</v>
@@ -13162,22 +13162,22 @@
     </row>
     <row r="353" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B353" s="82" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C353" s="135">
         <v>1</v>
       </c>
       <c r="D353" s="82" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E353" s="135">
         <v>4</v>
       </c>
       <c r="F353" s="82" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G353" s="82" t="s">
         <v>68</v>
@@ -13186,22 +13186,22 @@
     </row>
     <row r="354" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B354" s="82" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C354" s="135">
         <v>1</v>
       </c>
       <c r="D354" s="82" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E354" s="135">
         <v>4</v>
       </c>
       <c r="F354" s="82" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G354" s="82" t="s">
         <v>68</v>
@@ -13210,16 +13210,16 @@
     </row>
     <row r="355" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B355" s="82" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C355" s="135">
         <v>2</v>
       </c>
       <c r="D355" s="82" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E355" s="135">
         <v>5</v>
@@ -13234,22 +13234,22 @@
     </row>
     <row r="356" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B356" s="82" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C356" s="135">
         <v>2</v>
       </c>
       <c r="D356" s="82" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E356" s="135">
         <v>4</v>
       </c>
       <c r="F356" s="82" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G356" s="82" t="s">
         <v>68</v>
@@ -13258,16 +13258,16 @@
     </row>
     <row r="357" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B357" s="83" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C357" s="135">
         <v>2</v>
       </c>
       <c r="D357" s="82" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E357" s="135">
         <v>5</v>
@@ -13276,7 +13276,7 @@
         <v>597</v>
       </c>
       <c r="G357" s="82" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H357" s="82"/>
     </row>
@@ -13301,7 +13301,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="151" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B1" s="151"/>
     </row>
@@ -13323,15 +13323,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005721397A3BFE5A4A917419C7A83AC783" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="307a94388e56e9751a6fa75618518c9e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc38967a-e624-4692-8609-7b3876446348" xmlns:ns3="5fa3040f-f19d-450a-bd88-cb580603c825" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d7536184872160fa59988b8cd14df01a" ns2:_="" ns3:_="">
     <xsd:import namespace="cc38967a-e624-4692-8609-7b3876446348"/>
@@ -13508,6 +13499,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EF9F981-0076-4364-BDD7-A50D169722D0}">
   <ds:schemaRefs>
@@ -13518,14 +13518,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2400F2D-550C-4C35-9776-BA0069A68A30}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF465B5B-EB50-4439-9704-1E1FDA5BE193}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13542,4 +13534,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2400F2D-550C-4C35-9776-BA0069A68A30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/risks.xlsx
+++ b/risks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\moodle\local\activities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF01C149-A4DD-4D60-BEC1-DE50F6FDED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B28854-8EC6-4881-9B7D-6C612A66767E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Risks" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="937">
   <si>
     <t>Classification</t>
   </si>
@@ -4327,9 +4327,6 @@
   </si>
   <si>
     <t>LOCATION - Off Campus Event</t>
-  </si>
-  <si>
-    <t>LOCATION - On Campus Event</t>
   </si>
   <si>
     <t>Events || LOCATION - Off Campus Event</t>
@@ -5235,7 +5232,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -5496,7 +5493,7 @@
     </row>
     <row r="13" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>48</v>
@@ -5519,7 +5516,7 @@
     </row>
     <row r="14" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>52</v>
@@ -5542,7 +5539,7 @@
     </row>
     <row r="15" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>56</v>
@@ -5565,7 +5562,7 @@
     </row>
     <row r="16" spans="1:9" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>59</v>
@@ -5660,7 +5657,7 @@
     </row>
     <row r="20" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>72</v>
@@ -5683,7 +5680,7 @@
     </row>
     <row r="21" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>74</v>
@@ -5706,7 +5703,7 @@
     </row>
     <row r="22" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>77</v>
@@ -5729,7 +5726,7 @@
     </row>
     <row r="23" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>79</v>
@@ -5752,7 +5749,7 @@
     </row>
     <row r="24" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>81</v>
@@ -6325,7 +6322,7 @@
     </row>
     <row r="48" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>144</v>
@@ -6348,7 +6345,7 @@
     </row>
     <row r="49" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>148</v>
@@ -6371,7 +6368,7 @@
     </row>
     <row r="50" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>150</v>
@@ -6394,7 +6391,7 @@
     </row>
     <row r="51" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>152</v>
@@ -6417,7 +6414,7 @@
     </row>
     <row r="52" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>154</v>
@@ -6440,7 +6437,7 @@
     </row>
     <row r="53" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>156</v>
@@ -6463,7 +6460,7 @@
     </row>
     <row r="54" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>160</v>
@@ -6486,7 +6483,7 @@
     </row>
     <row r="55" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>163</v>
@@ -6509,7 +6506,7 @@
     </row>
     <row r="56" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>166</v>
@@ -6532,7 +6529,7 @@
     </row>
     <row r="57" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>169</v>
@@ -6555,7 +6552,7 @@
     </row>
     <row r="58" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>171</v>
@@ -6578,7 +6575,7 @@
     </row>
     <row r="59" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>173</v>
@@ -6601,7 +6598,7 @@
     </row>
     <row r="60" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>176</v>
@@ -6624,7 +6621,7 @@
     </row>
     <row r="61" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>178</v>
@@ -6647,7 +6644,7 @@
     </row>
     <row r="62" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>181</v>
@@ -6670,7 +6667,7 @@
     </row>
     <row r="63" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>48</v>
@@ -6693,7 +6690,7 @@
     </row>
     <row r="64" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>185</v>
@@ -6716,7 +6713,7 @@
     </row>
     <row r="65" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>187</v>
@@ -6739,7 +6736,7 @@
     </row>
     <row r="66" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>190</v>
@@ -6762,7 +6759,7 @@
     </row>
     <row r="67" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>192</v>
@@ -6785,7 +6782,7 @@
     </row>
     <row r="68" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>195</v>
@@ -6808,7 +6805,7 @@
     </row>
     <row r="69" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>197</v>
@@ -6831,7 +6828,7 @@
     </row>
     <row r="70" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>200</v>
@@ -6854,7 +6851,7 @@
     </row>
     <row r="71" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>202</v>
@@ -6877,7 +6874,7 @@
     </row>
     <row r="72" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>204</v>
@@ -6900,7 +6897,7 @@
     </row>
     <row r="73" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>206</v>
@@ -6923,7 +6920,7 @@
     </row>
     <row r="74" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>208</v>
@@ -6946,7 +6943,7 @@
     </row>
     <row r="75" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>210</v>
@@ -6969,7 +6966,7 @@
     </row>
     <row r="76" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>212</v>
@@ -6992,7 +6989,7 @@
     </row>
     <row r="77" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>214</v>
@@ -7015,7 +7012,7 @@
     </row>
     <row r="78" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>216</v>
@@ -7038,7 +7035,7 @@
     </row>
     <row r="79" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>218</v>
@@ -7061,7 +7058,7 @@
     </row>
     <row r="80" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>221</v>
@@ -7084,7 +7081,7 @@
     </row>
     <row r="81" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>223</v>
@@ -7107,7 +7104,7 @@
     </row>
     <row r="82" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>225</v>
@@ -7130,7 +7127,7 @@
     </row>
     <row r="83" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>227</v>
@@ -7153,7 +7150,7 @@
     </row>
     <row r="84" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>229</v>
@@ -7176,7 +7173,7 @@
     </row>
     <row r="85" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>232</v>
@@ -7199,7 +7196,7 @@
     </row>
     <row r="86" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>234</v>
@@ -7222,7 +7219,7 @@
     </row>
     <row r="87" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>236</v>
@@ -7245,7 +7242,7 @@
     </row>
     <row r="88" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>238</v>
@@ -7268,7 +7265,7 @@
     </row>
     <row r="89" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>240</v>
@@ -7291,7 +7288,7 @@
     </row>
     <row r="90" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>242</v>
@@ -7314,7 +7311,7 @@
     </row>
     <row r="91" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>244</v>
@@ -7337,7 +7334,7 @@
     </row>
     <row r="92" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>246</v>
@@ -7360,7 +7357,7 @@
     </row>
     <row r="93" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>248</v>
@@ -7383,7 +7380,7 @@
     </row>
     <row r="94" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>250</v>
@@ -7406,7 +7403,7 @@
     </row>
     <row r="95" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>252</v>
@@ -7429,7 +7426,7 @@
     </row>
     <row r="96" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>256</v>
@@ -7452,7 +7449,7 @@
     </row>
     <row r="97" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>259</v>
@@ -7461,7 +7458,7 @@
         <v>4</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E97" s="4">
         <v>5</v>
@@ -7475,7 +7472,7 @@
     </row>
     <row r="98" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>261</v>
@@ -7498,7 +7495,7 @@
     </row>
     <row r="99" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>238</v>
@@ -7521,7 +7518,7 @@
     </row>
     <row r="100" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>264</v>
@@ -7545,7 +7542,7 @@
     </row>
     <row r="101" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>266</v>
@@ -7568,7 +7565,7 @@
     </row>
     <row r="102" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>268</v>
@@ -7591,7 +7588,7 @@
     </row>
     <row r="103" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>271</v>
@@ -7614,7 +7611,7 @@
     </row>
     <row r="104" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>273</v>
@@ -7637,7 +7634,7 @@
     </row>
     <row r="105" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>275</v>
@@ -7660,7 +7657,7 @@
     </row>
     <row r="106" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>278</v>
@@ -7683,7 +7680,7 @@
     </row>
     <row r="107" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>280</v>
@@ -7706,7 +7703,7 @@
     </row>
     <row r="108" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>282</v>
@@ -7729,7 +7726,7 @@
     </row>
     <row r="109" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>284</v>
@@ -7752,7 +7749,7 @@
     </row>
     <row r="110" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>286</v>
@@ -7775,7 +7772,7 @@
     </row>
     <row r="111" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>289</v>
@@ -7798,7 +7795,7 @@
     </row>
     <row r="112" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B112" s="9" t="s">
         <v>72</v>
@@ -7821,7 +7818,7 @@
     </row>
     <row r="113" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>74</v>
@@ -7844,7 +7841,7 @@
     </row>
     <row r="114" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>229</v>
@@ -7867,7 +7864,7 @@
     </row>
     <row r="115" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>296</v>
@@ -7890,7 +7887,7 @@
     </row>
     <row r="116" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>299</v>
@@ -7913,7 +7910,7 @@
     </row>
     <row r="117" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>302</v>
@@ -7936,7 +7933,7 @@
     </row>
     <row r="118" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>304</v>
@@ -7959,7 +7956,7 @@
     </row>
     <row r="119" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>306</v>
@@ -7982,7 +7979,7 @@
     </row>
     <row r="120" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>308</v>
@@ -8005,7 +8002,7 @@
     </row>
     <row r="121" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>310</v>
@@ -8028,7 +8025,7 @@
     </row>
     <row r="122" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>312</v>
@@ -8051,7 +8048,7 @@
     </row>
     <row r="123" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>314</v>
@@ -8074,7 +8071,7 @@
     </row>
     <row r="124" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>48</v>
@@ -8097,7 +8094,7 @@
     </row>
     <row r="125" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>316</v>
@@ -8120,7 +8117,7 @@
     </row>
     <row r="126" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>318</v>
@@ -8137,7 +8134,7 @@
     </row>
     <row r="127" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>320</v>
@@ -8157,7 +8154,7 @@
     </row>
     <row r="128" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>322</v>
@@ -8180,7 +8177,7 @@
     </row>
     <row r="129" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>325</v>
@@ -8203,7 +8200,7 @@
     </row>
     <row r="130" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>328</v>
@@ -8226,7 +8223,7 @@
     </row>
     <row r="131" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>330</v>
@@ -8249,7 +8246,7 @@
     </row>
     <row r="132" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>332</v>
@@ -8272,7 +8269,7 @@
     </row>
     <row r="133" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>334</v>
@@ -8295,7 +8292,7 @@
     </row>
     <row r="134" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>336</v>
@@ -8319,7 +8316,7 @@
     </row>
     <row r="135" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>240</v>
@@ -8343,7 +8340,7 @@
     </row>
     <row r="136" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>65</v>
@@ -8366,7 +8363,7 @@
     </row>
     <row r="137" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>340</v>
@@ -8389,7 +8386,7 @@
     </row>
     <row r="138" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>342</v>
@@ -8412,7 +8409,7 @@
     </row>
     <row r="139" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>344</v>
@@ -8435,7 +8432,7 @@
     </row>
     <row r="140" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>346</v>
@@ -8458,7 +8455,7 @@
     </row>
     <row r="141" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>348</v>
@@ -8481,7 +8478,7 @@
     </row>
     <row r="142" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>351</v>
@@ -8504,7 +8501,7 @@
     </row>
     <row r="143" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>353</v>
@@ -8527,7 +8524,7 @@
     </row>
     <row r="144" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>355</v>
@@ -8550,7 +8547,7 @@
     </row>
     <row r="145" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>358</v>
@@ -8573,7 +8570,7 @@
     </row>
     <row r="146" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>360</v>
@@ -8596,7 +8593,7 @@
     </row>
     <row r="147" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>238</v>
@@ -8619,7 +8616,7 @@
     </row>
     <row r="148" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>363</v>
@@ -8642,7 +8639,7 @@
     </row>
     <row r="149" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>365</v>
@@ -8665,7 +8662,7 @@
     </row>
     <row r="150" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>367</v>
@@ -8688,7 +8685,7 @@
     </row>
     <row r="151" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>369</v>
@@ -8711,7 +8708,7 @@
     </row>
     <row r="152" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>373</v>
@@ -8734,7 +8731,7 @@
     </row>
     <row r="153" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>377</v>
@@ -8757,7 +8754,7 @@
     </row>
     <row r="154" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>380</v>
@@ -8780,7 +8777,7 @@
     </row>
     <row r="155" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>382</v>
@@ -8803,7 +8800,7 @@
     </row>
     <row r="156" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>384</v>
@@ -8826,7 +8823,7 @@
     </row>
     <row r="157" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>386</v>
@@ -8849,7 +8846,7 @@
     </row>
     <row r="158" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>388</v>
@@ -8872,7 +8869,7 @@
     </row>
     <row r="159" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>240</v>
@@ -8895,7 +8892,7 @@
     </row>
     <row r="160" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>391</v>
@@ -8918,7 +8915,7 @@
     </row>
     <row r="161" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>394</v>
@@ -8941,7 +8938,7 @@
     </row>
     <row r="162" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>397</v>
@@ -8964,7 +8961,7 @@
     </row>
     <row r="163" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>400</v>
@@ -8987,7 +8984,7 @@
     </row>
     <row r="164" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>402</v>
@@ -9010,7 +9007,7 @@
     </row>
     <row r="165" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>232</v>
@@ -9033,7 +9030,7 @@
     </row>
     <row r="166" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>405</v>
@@ -9056,7 +9053,7 @@
     </row>
     <row r="167" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>407</v>
@@ -9079,7 +9076,7 @@
     </row>
     <row r="168" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>340</v>
@@ -9102,7 +9099,7 @@
     </row>
     <row r="169" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>411</v>
@@ -9125,7 +9122,7 @@
     </row>
     <row r="170" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>413</v>
@@ -9148,7 +9145,7 @@
     </row>
     <row r="171" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>415</v>
@@ -9171,7 +9168,7 @@
     </row>
     <row r="172" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>417</v>
@@ -9194,7 +9191,7 @@
     </row>
     <row r="173" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>419</v>
@@ -9217,7 +9214,7 @@
     </row>
     <row r="174" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>422</v>
@@ -9240,7 +9237,7 @@
     </row>
     <row r="175" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>424</v>
@@ -9263,7 +9260,7 @@
     </row>
     <row r="176" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>426</v>
@@ -9286,7 +9283,7 @@
     </row>
     <row r="177" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>417</v>
@@ -9309,7 +9306,7 @@
     </row>
     <row r="178" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>429</v>
@@ -9333,7 +9330,7 @@
     </row>
     <row r="179" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>431</v>
@@ -9357,7 +9354,7 @@
     </row>
     <row r="180" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>433</v>
@@ -9381,7 +9378,7 @@
     </row>
     <row r="181" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>435</v>
@@ -9405,7 +9402,7 @@
     </row>
     <row r="182" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>437</v>
@@ -9507,7 +9504,7 @@
         <v>4</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E186" s="4">
         <v>5</v>
@@ -11255,7 +11252,7 @@
     </row>
     <row r="262" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>586</v>
@@ -11278,7 +11275,7 @@
     </row>
     <row r="263" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>589</v>
@@ -11301,7 +11298,7 @@
     </row>
     <row r="264" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>282</v>
@@ -11324,7 +11321,7 @@
     </row>
     <row r="265" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>594</v>
@@ -11347,7 +11344,7 @@
     </row>
     <row r="266" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>48</v>
@@ -11370,7 +11367,7 @@
     </row>
     <row r="267" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>52</v>
@@ -11393,7 +11390,7 @@
     </row>
     <row r="268" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>185</v>
@@ -11416,7 +11413,7 @@
     </row>
     <row r="269" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>598</v>
@@ -11439,7 +11436,7 @@
     </row>
     <row r="270" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>187</v>
@@ -11462,7 +11459,7 @@
     </row>
     <row r="271" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>320</v>
@@ -11485,7 +11482,7 @@
     </row>
     <row r="272" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>605</v>
@@ -11508,7 +11505,7 @@
     </row>
     <row r="273" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>607</v>
@@ -11531,7 +11528,7 @@
     </row>
     <row r="274" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>610</v>
@@ -11554,7 +11551,7 @@
     </row>
     <row r="275" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>612</v>
@@ -11577,7 +11574,7 @@
     </row>
     <row r="276" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>250</v>
@@ -11600,7 +11597,7 @@
     </row>
     <row r="277" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>140</v>
@@ -11623,7 +11620,7 @@
     </row>
     <row r="278" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>618</v>
@@ -11646,7 +11643,7 @@
     </row>
     <row r="279" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>586</v>
@@ -11669,7 +11666,7 @@
     </row>
     <row r="280" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>589</v>
@@ -11692,7 +11689,7 @@
     </row>
     <row r="281" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>626</v>
@@ -11715,7 +11712,7 @@
     </row>
     <row r="282" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>628</v>
@@ -11738,7 +11735,7 @@
     </row>
     <row r="283" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>630</v>
@@ -11761,7 +11758,7 @@
     </row>
     <row r="284" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>632</v>
@@ -11784,7 +11781,7 @@
     </row>
     <row r="285" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>282</v>
@@ -11807,7 +11804,7 @@
     </row>
     <row r="286" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>594</v>
@@ -11830,7 +11827,7 @@
     </row>
     <row r="287" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>638</v>
@@ -11853,7 +11850,7 @@
     </row>
     <row r="288" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>641</v>
@@ -11876,7 +11873,7 @@
     </row>
     <row r="289" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>643</v>
@@ -11899,7 +11896,7 @@
     </row>
     <row r="290" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>607</v>
@@ -11922,7 +11919,7 @@
     </row>
     <row r="291" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>48</v>
@@ -11945,7 +11942,7 @@
     </row>
     <row r="292" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>52</v>
@@ -11968,7 +11965,7 @@
     </row>
     <row r="293" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>646</v>
@@ -11991,7 +11988,7 @@
     </row>
     <row r="294" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>318</v>
@@ -12008,7 +12005,7 @@
     </row>
     <row r="295" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>320</v>
@@ -12028,7 +12025,7 @@
     </row>
     <row r="296" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>65</v>
@@ -12051,7 +12048,7 @@
     </row>
     <row r="297" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>649</v>
@@ -12074,7 +12071,7 @@
     </row>
     <row r="298" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>605</v>
@@ -12097,7 +12094,7 @@
     </row>
     <row r="299" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>322</v>
@@ -12120,7 +12117,7 @@
     </row>
     <row r="300" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>653</v>
@@ -12143,7 +12140,7 @@
     </row>
     <row r="301" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>655</v>
@@ -12166,7 +12163,7 @@
     </row>
     <row r="302" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>657</v>
@@ -12190,7 +12187,7 @@
     </row>
     <row r="303" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>334</v>
@@ -12213,7 +12210,7 @@
     </row>
     <row r="304" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>660</v>
@@ -12236,7 +12233,7 @@
     </row>
     <row r="305" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>662</v>
@@ -12259,7 +12256,7 @@
     </row>
     <row r="306" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>664</v>
@@ -12282,7 +12279,7 @@
     </row>
     <row r="307" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>81</v>
@@ -12305,7 +12302,7 @@
     </row>
     <row r="308" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>667</v>
@@ -12328,7 +12325,7 @@
     </row>
     <row r="309" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>286</v>
@@ -12351,7 +12348,7 @@
     </row>
     <row r="310" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>670</v>
@@ -12375,7 +12372,7 @@
     </row>
     <row r="311" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>388</v>
@@ -12398,7 +12395,7 @@
     </row>
     <row r="312" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>673</v>
@@ -12421,7 +12418,7 @@
     </row>
     <row r="313" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>676</v>
@@ -12444,7 +12441,7 @@
     </row>
     <row r="314" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>678</v>
@@ -12467,7 +12464,7 @@
     </row>
     <row r="315" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>142</v>
@@ -12490,7 +12487,7 @@
     </row>
     <row r="316" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>681</v>
@@ -12513,7 +12510,7 @@
     </row>
     <row r="317" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>683</v>
@@ -12536,7 +12533,7 @@
     </row>
     <row r="318" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>685</v>
@@ -12559,7 +12556,7 @@
     </row>
     <row r="319" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>687</v>
@@ -12583,7 +12580,7 @@
     </row>
     <row r="320" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>689</v>
@@ -12606,7 +12603,7 @@
     </row>
     <row r="321" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>691</v>
@@ -14420,7 +14417,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8648A3A-F8F4-440F-9973-B0C67B0FA433}">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5" customWidth="1"/>
@@ -14478,7 +14475,7 @@
     </row>
     <row r="5" spans="1:4" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C5" t="s">
         <v>840</v>
@@ -14489,7 +14486,7 @@
     </row>
     <row r="6" spans="1:4" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C6" t="s">
         <v>840</v>
@@ -14731,7 +14728,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="C28" t="s">
         <v>841</v>
@@ -14742,7 +14739,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C29" t="s">
         <v>841</v>
@@ -14753,7 +14750,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C30" t="s">
         <v>841</v>
@@ -14764,7 +14761,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>829</v>
+        <v>777</v>
       </c>
       <c r="C31" t="s">
         <v>841</v>
@@ -14775,7 +14772,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C32" t="s">
         <v>841</v>
@@ -14786,7 +14783,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C33" t="s">
         <v>841</v>
@@ -14797,7 +14794,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="C34" t="s">
         <v>841</v>
@@ -14808,7 +14805,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>772</v>
+        <v>782</v>
       </c>
       <c r="C35" t="s">
         <v>841</v>
@@ -14819,7 +14816,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C36" t="s">
         <v>841</v>
@@ -14830,7 +14827,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C37" t="s">
         <v>841</v>
@@ -14841,7 +14838,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C38" t="s">
         <v>841</v>
@@ -14852,7 +14849,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C39" t="s">
         <v>841</v>
@@ -14863,7 +14860,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C40" t="s">
         <v>841</v>
@@ -14874,7 +14871,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C41" t="s">
         <v>841</v>
@@ -14885,7 +14882,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="C42" t="s">
         <v>841</v>
@@ -14896,7 +14893,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C43" t="s">
         <v>841</v>
@@ -14907,7 +14904,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C44" t="s">
         <v>841</v>
@@ -14918,7 +14915,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C45" t="s">
         <v>841</v>
@@ -14929,7 +14926,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>811</v>
+        <v>815</v>
+      </c>
+      <c r="B46" t="s">
+        <v>839</v>
       </c>
       <c r="C46" t="s">
         <v>841</v>
@@ -14940,10 +14940,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>815</v>
-      </c>
-      <c r="B47" t="s">
-        <v>839</v>
+        <v>797</v>
       </c>
       <c r="C47" t="s">
         <v>841</v>
@@ -14954,7 +14951,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C48" t="s">
         <v>841</v>
@@ -14965,7 +14962,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C49" t="s">
         <v>841</v>
@@ -14976,7 +14973,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C50" t="s">
         <v>841</v>
@@ -14987,7 +14984,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="C51" t="s">
         <v>841</v>
@@ -14998,7 +14995,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="C52" t="s">
         <v>841</v>
@@ -15009,7 +15006,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C53" t="s">
         <v>841</v>
@@ -15020,7 +15017,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C54" t="s">
         <v>841</v>
@@ -15031,7 +15028,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C55" t="s">
         <v>841</v>
@@ -15042,7 +15039,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C56" t="s">
         <v>841</v>
@@ -15053,7 +15050,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C57" t="s">
         <v>841</v>
@@ -15064,7 +15061,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C58" t="s">
         <v>841</v>
@@ -15075,7 +15072,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C59" t="s">
         <v>841</v>
@@ -15086,7 +15083,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C60" t="s">
         <v>841</v>
@@ -15097,7 +15094,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C61" t="s">
         <v>841</v>
@@ -15108,7 +15105,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C62" t="s">
         <v>841</v>
@@ -15119,7 +15116,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C63" t="s">
         <v>841</v>
@@ -15130,7 +15127,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C64" t="s">
         <v>841</v>
@@ -15141,7 +15138,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C65" t="s">
         <v>841</v>
@@ -15152,7 +15149,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>818</v>
+        <v>819</v>
+      </c>
+      <c r="B66" t="s">
+        <v>838</v>
       </c>
       <c r="C66" t="s">
         <v>841</v>
@@ -15163,10 +15163,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>819</v>
-      </c>
-      <c r="B67" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C67" t="s">
         <v>841</v>
@@ -15177,7 +15174,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="C68" t="s">
         <v>841</v>
@@ -15188,7 +15185,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C69" t="s">
         <v>841</v>
@@ -15199,7 +15196,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>822</v>
+        <v>769</v>
       </c>
       <c r="C70" t="s">
         <v>841</v>
@@ -15210,7 +15207,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>769</v>
+        <v>827</v>
       </c>
       <c r="C71" t="s">
         <v>841</v>
@@ -15221,7 +15218,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="C72" t="s">
         <v>841</v>
@@ -15232,7 +15229,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C73" t="s">
         <v>841</v>
@@ -15243,7 +15240,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C74" t="s">
         <v>841</v>
@@ -15254,7 +15251,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="C75" t="s">
         <v>841</v>
@@ -15265,7 +15262,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="C76" t="s">
         <v>841</v>
@@ -15276,7 +15273,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C77" t="s">
         <v>841</v>
@@ -15287,7 +15284,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>832</v>
+        <v>790</v>
       </c>
       <c r="C78" t="s">
         <v>841</v>
@@ -15298,7 +15295,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="C79" t="s">
         <v>841</v>
@@ -15309,7 +15306,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>780</v>
+        <v>833</v>
       </c>
       <c r="C80" t="s">
         <v>841</v>
@@ -15320,23 +15317,12 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C81" t="s">
         <v>841</v>
       </c>
       <c r="D81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>834</v>
-      </c>
-      <c r="C82" t="s">
-        <v>841</v>
-      </c>
-      <c r="D82">
         <v>0</v>
       </c>
     </row>
